--- a/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/DataValidation_TextLength/output.xlsx
+++ b/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/DataValidation_TextLength/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R8cea5c5e4b944738"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R993a761f91e44ad7"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/DataValidation_TextLength/output.xlsx
+++ b/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/DataValidation_TextLength/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R993a761f91e44ad7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R545a121fde0543a2"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/DataValidation_TextLength/output.xlsx
+++ b/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/DataValidation_TextLength/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R545a121fde0543a2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R66fde1a34a404460"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/DataValidation_TextLength/output.xlsx
+++ b/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/DataValidation_TextLength/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R66fde1a34a404460"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R650374065fed492c"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/DataValidation_TextLength/output.xlsx
+++ b/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/DataValidation_TextLength/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R650374065fed492c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rc23a98def1ab4e17"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/DataValidation_TextLength/output.xlsx
+++ b/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/DataValidation_TextLength/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rc23a98def1ab4e17"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rc3795dab39db45c4"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/DataValidation_TextLength/output.xlsx
+++ b/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/DataValidation_TextLength/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rc3795dab39db45c4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rfc2a891823a24e93"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/DataValidation_TextLength/output.xlsx
+++ b/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/DataValidation_TextLength/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rfc2a891823a24e93"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R21abc6c3dfda4ec7"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/DataValidation_TextLength/output.xlsx
+++ b/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/DataValidation_TextLength/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R21abc6c3dfda4ec7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R46e26b99704f4870"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/DataValidation_TextLength/output.xlsx
+++ b/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/DataValidation_TextLength/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R46e26b99704f4870"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rce47676901924bd7"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/DataValidation_TextLength/output.xlsx
+++ b/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/DataValidation_TextLength/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rce47676901924bd7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R6d5979536a884a1f"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/DataValidation_TextLength/output.xlsx
+++ b/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/DataValidation_TextLength/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R6d5979536a884a1f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rae6365af944242a1"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/DataValidation_TextLength/output.xlsx
+++ b/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/DataValidation_TextLength/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rae6365af944242a1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R35a1039a635245e3"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/DataValidation_TextLength/output.xlsx
+++ b/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/DataValidation_TextLength/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R35a1039a635245e3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R9e73162c55c14aec"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/DataValidation_TextLength/output.xlsx
+++ b/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/DataValidation_TextLength/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R9e73162c55c14aec"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R4a84cb3239834716"/>
   </x:sheets>
 </x:workbook>
 </file>
